--- a/ig/DM-SIDOBA/ValueSet-jdv-j401-categorie-droit-prestation-ms.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-jdv-j401-categorie-droit-prestation-ms.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>Property</t>
   </si>
@@ -99,91 +99,16 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Concept</t>
+    <t>Operation</t>
+  </si>
+  <si>
+    <t>niveau</t>
+  </si>
+  <si>
+    <t>=</t>
   </si>
   <si>
     <t>1</t>
-  </si>
-  <si>
-    <t>AAH et CPR</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>ACFP et ACTP</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>AVA (Assurance vieillesse des aidants)</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Carte mobilité inclusion</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>PCH</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>AEEH et son complément</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>Orientation ESMS Enfants</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Orientation scolaire</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>Matériel pédagogique adapté</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Accompagnant des élèves en situation de handicap (AESH)</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Formation et insertion professionnelle</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>RQTH (Reconnaissance de la qualité de travailleur handicapé)</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>Orientation ESMS Adultes</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>Orientation vers un Pôle de compétences et de prestations externalisées (PCPE)</t>
   </si>
   <si>
     <t/>
@@ -456,7 +381,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -465,10 +390,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>22</v>
+      <c r="C1" t="s" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="2">
@@ -478,10 +406,13 @@
       <c r="B2" t="s" s="2">
         <v>30</v>
       </c>
+      <c r="C2" t="s" s="2">
+        <v>31</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
         <v>32</v>
@@ -493,110 +424,6 @@
       </c>
       <c r="B4" t="s" s="2">
         <v>34</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
